--- a/VerveStacks_IND_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IND_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_syn_5\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B272AD6D-0C7F-499E-AF3B-CEE5450DF237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E78AAEC8-0E76-49AB-AE7C-065D052C1B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AB8B7132-5001-4085-9813-3C83740988F4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B6C59ACB-BBF0-4B40-AECE-DD3BB14B4F39}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2191,7 +2191,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BEAB82C-549F-4D44-9F56-DD72A4F82431}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46363C7C-DDF9-42A4-9585-06DEC7AF1038}">
   <dimension ref="B3:L205"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IND_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IND_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_syn_5\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E78AAEC8-0E76-49AB-AE7C-065D052C1B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{28F0E580-B23F-41DE-96E6-7988C8CED36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B6C59ACB-BBF0-4B40-AECE-DD3BB14B4F39}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CD891BB2-D076-402D-88D2-3C9255F40799}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2191,7 +2191,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46363C7C-DDF9-42A4-9585-06DEC7AF1038}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B3FC9E4-1B72-4E37-BC9F-B5F9114AB4AF}">
   <dimension ref="B3:L205"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IND_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IND_grids_syn_5/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_syn_5\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28F0E580-B23F-41DE-96E6-7988C8CED36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A084578-307E-4F4F-895E-657557828FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CD891BB2-D076-402D-88D2-3C9255F40799}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EFD989A6-A7E5-4C58-BD6E-097FD5EE5B4B}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2191,7 +2191,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B3FC9E4-1B72-4E37-BC9F-B5F9114AB4AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F42BF53-DBE4-4C66-A07C-7E440E33CED9}">
   <dimension ref="B3:L205"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
